--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-patient.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -484,14 +484,6 @@
 　- 1020 ヒンドゥー教  
 　- 1023 イスラム教  
 など</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace</t>
@@ -538,6 +530,14 @@
 　- 2111-3 フランス人  
 　- 2112-1 ドイツ人  
 など</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -3405,10 +3405,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3428,13 +3428,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>136</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>82</v>
@@ -3456,16 +3456,16 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3524,10 +3524,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3547,13 +3547,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>136</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3575,16 +3575,16 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3643,10 +3643,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -5057,7 +5057,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>259</v>
